--- a/data/accounts_registry.xlsx
+++ b/data/accounts_registry.xlsx
@@ -489,42 +489,42 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>rjrrk ej'</t>
+          <t>3tt3t3t3t</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>+77700042874</t>
+          <t>+77004287470</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Работник</t>
+          <t>Выпускник</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
+          <t>Инженерные технологии</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>6B11380 - Вычислительная техника и программное обеспечение</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>vtpo 25-</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>approved</t>
+          <t>pending</t>
         </is>
       </c>
     </row>

--- a/data/accounts_registry.xlsx
+++ b/data/accounts_registry.xlsx
@@ -9,7 +9,9 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Applicants" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Applicants'!$A$1:$L$11</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -413,8 +415,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
+    <col width="6" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -429,47 +445,52 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Telegram Profile</t>
+          <t>Ссылка Telegram</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Full Name</t>
+          <t>ФИО</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Телефон</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Role</t>
+          <t>Роль</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Faculty</t>
+          <t>Кафедра</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Specialty</t>
+          <t>Специальность</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Course</t>
+          <t>Курс</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>Group</t>
+          <t>Группа</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>Registration Status</t>
+          <t>Грантник</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Статус регистрации</t>
         </is>
       </c>
     </row>
@@ -489,7 +510,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3tt3t3t3t</t>
+          <t>etetetet</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -499,7 +520,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Выпускник</t>
+          <t>Студент</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -514,21 +535,433 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>vtpo 25-</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>pending</t>
+          <t>ВТПО 23-1</t>
+        </is>
+      </c>
+      <c r="K2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1216962667</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ilikebooobs</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>https://t.me/ilikebooobs</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Ильяс Ильясович Ильясулы</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>+77756277881</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Студент</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Инженерные технологии</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>6B11380 - Вычислительная техника и программное обеспечение</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>ВТПО 23-1</t>
+        </is>
+      </c>
+      <c r="K3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+    </row>
+    <row r="4"/>
+    <row r="5"/>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1216962667</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ilikebooobs</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://t.me/ilikebooobs</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>бубу Кадыров</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>+77756277881</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Работник</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K6" t="b">
+        <v>0</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1216962667</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ilikebooobs</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://t.me/ilikebooobs</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>бубу Кадыров</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>+77756277881</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Работник</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K7" t="b">
+        <v>0</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1216962667</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ilikebooobs</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>https://t.me/ilikebooobs</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>бубу Кадыров</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>+77756277881</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Работник</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K8" t="b">
+        <v>0</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1216962667</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ilikebooobs</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>https://t.me/ilikebooobs</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>бубу Кадыров</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>+77756277881</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Работник</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K9" t="b">
+        <v>0</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1216962667</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ilikebooobs</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>https://t.me/ilikebooobs</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>бубу Кадыров</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>+77756277881</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Работник</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K10" t="b">
+        <v>0</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1216962667</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>ilikebooobs</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>https://t.me/ilikebooobs</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>бубу Кадыров</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>+77756277881</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Работник</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K11" t="b">
+        <v>1</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>approved</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:L11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/accounts_registry.xlsx
+++ b/data/accounts_registry.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Applicants" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Applicants'!$A$1:$L$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Applicants'!$A$1:$L$19</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -465,7 +465,7 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Кафедра</t>
+          <t>Бірлестік / кафедра</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
@@ -510,7 +510,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>etetetet</t>
+          <t>grgrgrg</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -554,63 +554,120 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
+        <v>7939104831</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>kotakbaser</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>https://t.me/kotakbaser</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>hdhdhdd</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>+77003272517</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Студент</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Инженерные технологии</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>6B11380 - Вычислительная техника и программное обеспечение</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>ВТПО 23-1</t>
+        </is>
+      </c>
+      <c r="K3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
         <v>1216962667</v>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>ilikebooobs</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>https://t.me/ilikebooobs</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Ильяс Ильясович Ильясулы</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>+77756277881</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Студент</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>Инженерные технологии</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>6B11380 - Вычислительная техника и программное обеспечение</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>ВТПО 23-1</t>
         </is>
       </c>
-      <c r="K3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>approved</t>
-        </is>
-      </c>
-    </row>
-    <row r="4"/>
+      <c r="K4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+    </row>
     <row r="5"/>
     <row r="6">
       <c r="A6" t="n">
@@ -952,16 +1009,480 @@
         </is>
       </c>
       <c r="K11" t="b">
+        <v>0</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1216962667</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>ilikebooobs</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>https://t.me/ilikebooobs</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>бубу Кадыров</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>+77756277881</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Работник</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K12" t="b">
+        <v>0</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>1216962667</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ilikebooobs</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>https://t.me/ilikebooobs</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>бубу Кадыров</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>+77756277881</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Работник</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K13" t="b">
+        <v>0</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>1216962667</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ilikebooobs</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>https://t.me/ilikebooobs</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>бубу Кадыров</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>+77756277881</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Работник</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K14" t="b">
+        <v>0</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>1216962667</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ilikebooobs</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>https://t.me/ilikebooobs</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>бубу Кадыров</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>+77756277881</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Работник</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K15" t="b">
+        <v>0</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>1216962667</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ilikebooobs</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>https://t.me/ilikebooobs</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>бубу Кадыров</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>+77756277881</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Работник</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K16" t="b">
+        <v>0</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>1216962667</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>ilikebooobs</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>https://t.me/ilikebooobs</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>бубу Кадыров</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>+77756277881</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Работник</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K17" t="b">
+        <v>0</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>1216962667</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>ilikebooobs</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>https://t.me/ilikebooobs</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>бубу Кадыров</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>+77756277881</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Работник</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K18" t="b">
+        <v>0</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>1216962667</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>ilikebooobs</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>https://t.me/ilikebooobs</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>бубу Кадыров</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>+77756277881</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Работник</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K19" t="b">
         <v>1</v>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L11"/>
+  <autoFilter ref="A1:L19"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/accounts_registry.xlsx
+++ b/data/accounts_registry.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Applicants" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Applicants'!$A$1:$L$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Applicants'!$A$1:$L$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -566,31 +566,31 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1216962667</v>
+        <v>7939104831</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ilikebooobs</t>
+          <t>kotakbaser</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://t.me/ilikebooobs</t>
+          <t>https://t.me/kotakbaser</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Ильяс Ильясович Ильясулы</t>
+          <t>hdhdjd</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>+77756277881</t>
+          <t>+77011234567</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Студент</t>
+          <t>Преподаватель</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -605,12 +605,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>ВТПО 23-1</t>
+          <t>втпо 23-1</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr">
@@ -626,26 +626,26 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>7939104831</v>
+        <v>5394280567</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>kotakbaser</t>
+          <t>spisoq</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://t.me/kotakbaser</t>
+          <t>https://t.me/spisoq</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>hdhdjd</t>
+          <t>fefefefe\</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>+77011234567</t>
+          <t>+77004287470</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -660,7 +660,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6B11380 - Вычислительная техника и программное обеспечение</t>
+          <t>6B07155 - Электроэнергетика</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -670,7 +670,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>втпо 23-1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K4" s="1" t="inlineStr">
@@ -807,69 +807,12 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>7939104831</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>kotakbaser</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>https://t.me/kotakbaser</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>hdhdjd</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>+77011234567</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Преподаватель</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Инженерные технологии</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>6B11380 - Вычислительная техника и программное обеспечение</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>втпо 23-1</t>
-        </is>
-      </c>
-      <c r="K8" s="1" t="inlineStr">
-        <is>
-          <t>Нет ❌</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>approved</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:L8"/>
-  <dataValidations count="5">
+  <autoFilter ref="A1:L7"/>
+  <dataValidations count="6">
+    <dataValidation sqref="K2:K5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" error="Выберите значение из списка" prompt="Грантник: Да ✅ или Нет ❌" type="list">
+      <formula1>"Да ✅,Нет ❌"</formula1>
+    </dataValidation>
     <dataValidation sqref="K2:K5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" error="Выберите значение из списка" prompt="Грантник: Да ✅ или Нет ❌" type="list">
       <formula1>"Да ✅,Нет ❌"</formula1>
     </dataValidation>
